--- a/backup_1cr_tenders.xlsx
+++ b/backup_1cr_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5094.</t>
+          <t>5218.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>243.</t>
+          <t>250.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1656.</t>
+          <t>1786.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3848.</t>
+          <t>3976.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4070.</t>
+          <t>4197.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4094.</t>
+          <t>4221.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5248.</t>
+          <t>5372.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2700.</t>
+          <t>2829.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1392.</t>
+          <t>1406.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/backup_1cr_tenders.xlsx
+++ b/backup_1cr_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5218.</t>
+          <t>5375.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -544,53 +544,53 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Uttarakhand eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>250.</t>
+          <t>2370.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>08-Jun-2026 09:00 AM</t>
+          <t>10-Jun-2026 04:50 PM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15-Jun-2026 02:00 PM</t>
+          <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15-Jun-2026 03:00 PM</t>
+          <t>03-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of Chief Engineer (Distribution) Garhwal Zone, Office Building and Other Misc. Civil Works at 18 E.C. Road, UPCL Campus, Dehradun.] [ECC-17/2026-27][2026_UPCL8_96394_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MD - UPCL||CE (Civil)||SE (Civil)</t>
+          <t>Medical and Health</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1,20,79,891</t>
+          <t>5,00,00,000</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12079891</v>
+        <v>50000000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SnkkmSbr53KLUrrNIrRVrNQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -610,32 +610,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1786.</t>
+          <t>4404.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10-Jun-2026 04:50 PM</t>
+          <t>04-Jun-2026 05:05 PM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Medical and Health</t>
+          <t>Medical and Health||Chief Engineer</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -668,27 +668,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3976.</t>
+          <t>4566.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>04-Jun-2026 05:05 PM</t>
+          <t>04-Jun-2026 10:00 AM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24-Jun-2026 06:00 PM</t>
+          <t>23-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4197.</t>
+          <t>4577.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>04-Jun-2026 10:00 AM</t>
+          <t>04-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -784,27 +784,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4221.</t>
+          <t>5517.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>04-Jun-2026 09:00 AM</t>
+          <t>08-May-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23-Jun-2026 06:00 PM</t>
+          <t>18-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>19-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -842,27 +842,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5372.</t>
+          <t>3378.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08-May-2026 09:00 AM</t>
+          <t>08-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18-Jun-2026 06:00 PM</t>
+          <t>29-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19-Jun-2026 11:00 AM</t>
+          <t>30-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -872,15 +872,15 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>4,48,00,000</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>50000000</v>
+        <v>44800000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -900,101 +900,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2829.</t>
+          <t>1375.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08-Jun-2026 04:00 PM</t>
+          <t>03-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29-Jun-2026 06:00 PM</t>
+          <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>30-Jun-2026 01:00 PM</t>
+          <t>25-Jun-2026 06:05 PM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
+          <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4,48,00,000</t>
+          <t>1,30,03,957</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>44800000</v>
+        <v>13003957</v>
       </c>
       <c r="L9" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Central eProcure</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>10</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1406.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>03-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 06:05 PM</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1,30,03,957</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>13003957</v>
-      </c>
-      <c r="L10" t="inlineStr">
         <is>
           <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc6oEKlA0tALrMKwrkHr0%2Fg%3D%3D</t>
         </is>

--- a/backup_1cr_tenders.xlsx
+++ b/backup_1cr_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,457 +486,51 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5375.</t>
+          <t>1488.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21-May-2026 05:00 PM</t>
+          <t>03-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>25-Jun-2026 02:00 PM</t>
+          <t>25-Jun-2026 06:05 PM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+          <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1,34,50,000</t>
+          <t>1,30,03,957</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13450000</v>
+        <v>13003957</v>
       </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2370.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>10-Jun-2026 04:50 PM</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>02-Jul-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>03-Jul-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Medical and Health</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4404.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04-Jun-2026 05:05 PM</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4566.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>04-Jun-2026 10:00 AM</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>23-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>4577.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>04-Jun-2026 09:00 AM</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>23-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>5517.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>08-May-2026 09:00 AM</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>18-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>19-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>3378.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>08-Jun-2026 04:00 PM</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>29-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>30-Jun-2026 01:00 PM</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>4,48,00,000</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>44800000</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Central eProcure</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1375.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>03-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 06:05 PM</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>1,30,03,957</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>13003957</v>
-      </c>
-      <c r="L9" t="inlineStr">
         <is>
           <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc6oEKlA0tALrMKwrkHr0%2Fg%3D%3D</t>
         </is>

--- a/backup_1cr_tenders.xlsx
+++ b/backup_1cr_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1488.</t>
+          <t>1605.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/backup_1cr_tenders.xlsx
+++ b/backup_1cr_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,51 +486,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5692.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>21-May-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1,34,50,000</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>13450000</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4589.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10-Jun-2026 04:50 PM</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Medical and Health</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5346.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04-Jun-2026 05:05 PM</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5385.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>04-Jun-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5391.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5801.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>08-May-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5142.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>08-Jun-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4,48,00,000</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>44800000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Central eProcure</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C9" t="n">
         <v>10</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1605.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1807.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>03-Jun-2026 06:00 PM</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>25-Jun-2026 06:05 PM</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>1,30,03,957</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K9" t="n">
         <v>13003957</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc6oEKlA0tALrMKwrkHr0%2Fg%3D%3D</t>
         </is>

--- a/backup_1cr_tenders.xlsx
+++ b/backup_1cr_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5692.</t>
+          <t>5708.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4589.</t>
+          <t>4623.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5346.</t>
+          <t>5371.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5385.</t>
+          <t>5410.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5391.</t>
+          <t>5416.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5801.</t>
+          <t>5815.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5142.</t>
+          <t>5171.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1807.</t>
+          <t>1812.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/backup_1cr_tenders.xlsx
+++ b/backup_1cr_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5708.</t>
+          <t>5906.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4623.</t>
+          <t>4964.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5371.</t>
+          <t>5586.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5410.</t>
+          <t>5613.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5416.</t>
+          <t>5619.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5815.</t>
+          <t>6015.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5171.</t>
+          <t>5401.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1812.</t>
+          <t>1964.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/backup_1cr_tenders.xlsx
+++ b/backup_1cr_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5906.</t>
+          <t>5938.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4964.</t>
+          <t>4996.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5586.</t>
+          <t>5618.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5613.</t>
+          <t>5645.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5619.</t>
+          <t>5651.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6015.</t>
+          <t>6047.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5401.</t>
+          <t>5433.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1964.</t>
+          <t>1966.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/backup_1cr_tenders.xlsx
+++ b/backup_1cr_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5938.</t>
+          <t>6082.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4996.</t>
+          <t>5317.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5618.</t>
+          <t>5809.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5645.</t>
+          <t>5836.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5651.</t>
+          <t>5842.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6047.</t>
+          <t>6191.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5433.</t>
+          <t>5679.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1966.</t>
+          <t>2037.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/backup_1cr_tenders.xlsx
+++ b/backup_1cr_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6082.</t>
+          <t>5898.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5317.</t>
+          <t>5220.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5809.</t>
+          <t>5656.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5836.</t>
+          <t>5682.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5842.</t>
+          <t>5688.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6191.</t>
+          <t>6003.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5679.</t>
+          <t>5538.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2037.</t>
+          <t>2010.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/backup_1cr_tenders.xlsx
+++ b/backup_1cr_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5898.</t>
+          <t>5552.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5220.</t>
+          <t>5059.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5656.</t>
+          <t>5375.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5682.</t>
+          <t>5389.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5688.</t>
+          <t>5395.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6003.</t>
+          <t>5641.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5538.</t>
+          <t>5286.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2010.</t>
+          <t>2078.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/backup_1cr_tenders.xlsx
+++ b/backup_1cr_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -494,45 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5552.</t>
+          <t>158.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21-May-2026 05:00 PM</t>
+          <t>25-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>02-Jul-2026 12:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>25-Jun-2026 02:00 PM</t>
+          <t>02-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+          <t>[Renovation work for office building of Advocate General Haryana at Chandigarh (Deposite work) of Advocate General Haryana (Balance work)] [2026DDE39FAF 8F82 483C 9A02 6FF9DD62175F270HSV][2026_HBC_531909_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>Haryana Board Corporation||HUDA||PKL Division II</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1,34,50,000</t>
+          <t>1,98,80,991</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13450000</v>
+        <v>19880991</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc9eIaeYuAN%2FryxX3743FQg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -548,49 +548,49 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5059.</t>
+          <t>4807.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10-Jun-2026 04:50 PM</t>
+          <t>21-May-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>03-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Medical and Health</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>1,34,50,000</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>50000000</v>
+        <v>13450000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
         </is>
       </c>
     </row>
@@ -610,27 +610,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5375.</t>
+          <t>47.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04-Jun-2026 05:05 PM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24-Jun-2026 06:00 PM</t>
+          <t>15-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>16-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 11/2026-27 of EE M and Jodhpur][2026_MEDIC_570931_1]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SH1I9Tmt7tSMrYmTE2Aq0ow%3D%3D</t>
         </is>
       </c>
     </row>
@@ -668,27 +668,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5389.</t>
+          <t>205.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>04-Jun-2026 10:00 AM</t>
+          <t>25-Jun-2026 06:15 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23-Jun-2026 06:00 PM</t>
+          <t>12-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>13-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Bharatpur (Civil, Sanitary, Joinery works)] [NIT No.03/2026-27 EE M and H DivBharatpur/][2026_MEDIC_571221_1]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Si%2FvDRgEcsjwlBatNiPx9XA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -726,27 +726,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5395.</t>
+          <t>1297.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>04-Jun-2026 09:00 AM</t>
+          <t>23-Jun-2026 04:20 PM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23-Jun-2026 06:00 PM</t>
+          <t>15-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>16-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
+          <t>[Rate Contract for Electric Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Bharatpur ] [NIT No.05/2026-27 EE M and H DivBharatpur/][2026_MEDIC_570559_1]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Shv4Y3gc9rnanMu%2BlPBC1%2FA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5641.</t>
+          <t>4492.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>08-May-2026 09:00 AM</t>
+          <t>10-Jun-2026 04:50 PM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>Medical and Health</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5286.</t>
+          <t>4674.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08-Jun-2026 04:00 PM</t>
+          <t>04-Jun-2026 05:05 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>30-Jun-2026 01:00 PM</t>
+          <t>30-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -872,15 +872,15 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4,48,00,000</t>
+          <t>5,00,00,000</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>44800000</v>
+        <v>50000000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -900,45 +900,103 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2078.</t>
+          <t>4889.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>03-Jun-2026 06:00 PM</t>
+          <t>08-May-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24-Jun-2026 06:00 PM</t>
+          <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25-Jun-2026 06:05 PM</t>
+          <t>03-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
+          <t>Medical and Health||Chief Engineer</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1,30,03,957</t>
+          <t>5,00,00,000</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>13003957</v>
+        <v>50000000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc6oEKlA0tALrMKwrkHr0%2Fg%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4618.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>08-Jun-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4,48,00,000</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>44800000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
         </is>
       </c>
     </row>

--- a/backup_1cr_tenders.xlsx
+++ b/backup_1cr_tenders.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -494,45 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>158.</t>
+          <t>3277.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25-Jun-2026 06:00 PM</t>
+          <t>20-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02-Jul-2026 12:00 PM</t>
+          <t>24-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>02-Jul-2026 02:00 PM</t>
+          <t>25-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Renovation work for office building of Advocate General Haryana at Chandigarh (Deposite work) of Advocate General Haryana (Balance work)] [2026DDE39FAF 8F82 483C 9A02 6FF9DD62175F270HSV][2026_HBC_531909_1]</t>
+          <t>[Tender for the Procurement of Fully Automated immunodiagnostic system based on latest chemiluminesnce techniques on Reagents Rental Method] [1540_08.06.2026][2026_SMSMC_569861_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Haryana Board Corporation||HUDA||PKL Division II</t>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller||SMS Hospital Jaipur</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1,98,80,991</t>
+          <t>11,00,00,000</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>19880991</v>
+        <v>110000000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc9eIaeYuAN%2FryxX3743FQg%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SMx%2BQuPJrlNv%2FkvBqo5PTXg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -544,53 +544,53 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4807.</t>
+          <t>1224.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21-May-2026 05:00 PM</t>
+          <t>25-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01-Jul-2026 02:00 PM</t>
+          <t>13-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>03-Jul-2026 02:00 PM</t>
+          <t>13-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+          <t>[Construction of Community Centre on Bas-Bhangrola road in village Bhangrola in ward 06 under MC Manesar limit] [202614D22CA0 5C7D 4D88 AB43 52FC317DBA7B1809ULB][2026_HRY_531736_1]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>Haryana Government||Urban Local Bodies||MC Manesar</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1,34,50,000</t>
+          <t>7,68,83,803</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13450000</v>
+        <v>76883803</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sq8qQOlcAQqZnmVMKtZjagw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -606,36 +606,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.</t>
+          <t>4228.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>17-Apr-2026 12:30 PM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15-Jul-2026 06:00 PM</t>
+          <t>06-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16-Jul-2026 11:00 AM</t>
+          <t>07-Jul-2026 11:30 AM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 11/2026-27 of EE M and Jodhpur][2026_MEDIC_570931_1]</t>
+          <t>[Procurement of Gauge and Bandage for 02 years] [ENIB No 04 (2026-27)][2026_SPMCB_552196_1]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>S.P. Medical college, Bikaner||Principal, S.P.M.C., Bikaner||PBM A.G. HOSPITALS||SUPERINTENDENT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SH1I9Tmt7tSMrYmTE2Aq0ow%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Syw4F6SBZFGttK1HzsqKdgA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -660,40 +660,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Himachal eTenders</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>205.</t>
+          <t>101.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25-Jun-2026 06:15 PM</t>
+          <t>01-Jul-2026 05:30 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12-Jul-2026 06:00 PM</t>
+          <t>05-Aug-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13-Jul-2026 11:00 AM</t>
+          <t>07-Aug-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Bharatpur (Civil, Sanitary, Joinery works)] [NIT No.03/2026-27 EE M and H DivBharatpur/][2026_MEDIC_571221_1]</t>
+          <t>[Setting up of ASU and Supply of Medical oxygen] [E-tender of Air Separation Unit ][2026_DMER5_137839_1]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>Directorate of Medical Education and Research||Dr Rajendra Prasad Govt Medical College Tanda Kangra</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Si%2FvDRgEcsjwlBatNiPx9XA%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S5cZtX41mGcgxuk1aO1fnGg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -718,53 +718,53 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>JK eTenders</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1297.</t>
+          <t>3919.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23-Jun-2026 04:20 PM</t>
+          <t>01-Jun-2026 10:00 AM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15-Jul-2026 06:00 PM</t>
+          <t>11-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>16-Jul-2026 11:00 AM</t>
+          <t>13-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Rate Contract for Electric Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Bharatpur ] [NIT No.05/2026-27 EE M and H DivBharatpur/][2026_MEDIC_570559_1]</t>
+          <t>[DESIGN, SUPPLY, INSTALLATION, TESTING, COMMISSIONING OF HVAC SYSTEM AT TEACHING HOSPITAL, GOVERNMENT MEDICAL COLLEGE DODA] [e- NIT No.MHCJ/Tech/e-NIT/2026-27/04 ][2026_PWDJK_311243_1]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>PWD||CE MED Jammu||Mechanical Circle Jammu</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>4,97,94,781</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>50000000</v>
+        <v>49794781</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Shv4Y3gc9rnanMu%2BlPBC1%2FA%3D%3D</t>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Slx9M53hmIEhkOsQJDIct2w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4492.</t>
+          <t>3308.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10-Jun-2026 04:50 PM</t>
+          <t>20-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>06-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>07-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+          <t>[Purchase of desktop computer] [17/2267-73 Dated- 16/06/2026][2026_SMSMC_569061_1]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Medical and Health</t>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>1,96,59,000</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>50000000</v>
+        <v>19659000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SnCYS0i0gD4QMesbx3OsNAw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -834,53 +834,53 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4674.</t>
+          <t>868.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>04-Jun-2026 05:05 PM</t>
+          <t>26-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29-Jun-2026 06:00 PM</t>
+          <t>06-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>30-Jun-2026 11:00 AM</t>
+          <t>07-Jul-2026 10:00 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+          <t>[Const. of the building Mother and Child Block at Civil Hospital at Sonipat (Pdg. 01 No. 13 Passenger, 04 No. Bed Lift and 01 No. Dumbwaiter Lift). Recall] [202666510592 F004 436F ABE8 2656471BFB6E665BAR][2026_HRY_532088_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE (Elect.) Karnal||EE Elect. Karnal</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>1,58,60,000</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>50000000</v>
+        <v>15860000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SXqMf39QjSypa7kfuDJeRgA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -896,49 +896,49 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4889.</t>
+          <t>3320.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08-May-2026 09:00 AM</t>
+          <t>20-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>06-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>07-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+          <t>[Purchase of Echo machine with TEE machine for CTVS department] [28/2267-73 Dated- 16/06/2026][2026_SMSMC_569513_1]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>1,55,00,000</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>50000000</v>
+        <v>15500000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SDNIOm79HSPSzlXWxxPk90g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -954,49 +954,49 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4618.</t>
+          <t>2516.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08-Jun-2026 04:00 PM</t>
+          <t>24-Jun-2026 10:00 AM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29-Jun-2026 06:00 PM</t>
+          <t>07-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>30-Jun-2026 01:00 PM</t>
+          <t>09-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
+          <t>[Package 01/2026-27/Construction of Various Development works/Bus stand Building/CC Road/Toilet Block at RSRTC Hanumangarh Depot Distt Hanumangarh. ] [EE-RSAMB-HMH-NIT-06-2026-27][2026_RSAMB_570289_1]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>RSAMB||ACE - Zone II||S.E. - Circle SGNR||Ex.En. - Sriganganagar</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4,48,00,000</t>
+          <t>1,36,37,000</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>44800000</v>
+        <v>13637000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Svv%2BeP0mqARZt1Jkx%2BRZgig%3D%3D</t>
         </is>
       </c>
     </row>
